--- a/data/2022_SEP_Resumen_Graficos.xlsx
+++ b/data/2022_SEP_Resumen_Graficos.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aviva\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aviva\Documents\Analisis-tesis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD56735-3D44-493C-A54D-D4555421074C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20715" windowHeight="13275"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FENOLOGIA" sheetId="6" r:id="rId1"/>
@@ -25,7 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">FENOLOGIA!$A$1:$F$25</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -393,8 +394,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -441,6 +442,12 @@
       <color rgb="FF000000"/>
       <name val="Liberation Serif"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -470,7 +477,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -492,11 +499,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -504,11 +511,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
-    <cellStyle name="Normal 3" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -810,9 +818,9 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="12700" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1"/>
+                <a:srgbClr val="7030A0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -825,7 +833,7 @@
               <a:solidFill>
                 <a:srgbClr val="7030A0"/>
               </a:solidFill>
-              <a:ln w="15875">
+              <a:ln w="28575">
                 <a:solidFill>
                   <a:srgbClr val="7030A0"/>
                 </a:solidFill>
@@ -955,7 +963,7 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1018,7 +1026,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -1028,7 +1036,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="es-ES" sz="1800" b="1" baseline="30000">
+                  <a:rPr lang="es-ES" sz="2400" b="1" baseline="30000">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -1038,7 +1046,7 @@
                   <a:t>Mean</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="es-ES" sz="1800" b="1" baseline="0">
+                  <a:rPr lang="es-ES" sz="2400" b="1" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
@@ -1048,14 +1056,14 @@
                   <a:t> </a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="es-ES" sz="1800" b="1" baseline="30000">
+                  <a:rPr lang="es-ES" sz="2400" b="1" baseline="30000">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
                     <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:rPr>
-                  <a:t>density ( ± SD) of Aphrophoridae nymphs</a:t>
+                  <a:t>density ( ± s.e) ofAphrophoridae nymphs</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1064,8 +1072,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="2.8011275089626628E-2"/>
-              <c:y val="9.1776348150100384E-2"/>
+              <c:x val="9.300576821986652E-3"/>
+              <c:y val="7.9494940296739258E-2"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1081,7 +1089,7 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="2000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
@@ -1110,13 +1118,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="es-ES"/>
@@ -1142,36 +1150,35 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
-                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="es-ES" sz="1600" b="1" i="0" baseline="0">
+                  <a:rPr lang="es-ES" sz="1800" b="1" i="0" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1"/>
                     </a:solidFill>
-                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:rPr>
                   <a:t>Adults captured</a:t>
                 </a:r>
-                <a:endParaRPr lang="es-ES" sz="1600" b="1" i="0">
+                <a:endParaRPr lang="es-ES" sz="1800" b="1" i="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
-                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1185,13 +1192,13 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1"/>
                   </a:solidFill>
-                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="es-ES"/>
@@ -1214,13 +1221,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1050" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1"/>
                 </a:solidFill>
-                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="es-ES"/>
@@ -1250,9 +1257,9 @@
       </c:catAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="12700">
           <a:solidFill>
-            <a:schemeClr val="tx1"/>
+            <a:schemeClr val="bg1"/>
           </a:solidFill>
         </a:ln>
         <a:effectLst/>
@@ -1300,7 +1307,6 @@
           </a:p>
         </c:txPr>
       </c:legendEntry>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:solidFill>
@@ -1331,7 +1337,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1339,6 +1344,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:noFill/>
@@ -3631,7 +3637,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3639,6 +3644,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3743,7 +3749,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -8775,7 +8781,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="es-ES"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -10641,7 +10647,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -10649,6 +10654,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11232,7 +11238,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -11341,7 +11346,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -11439,7 +11443,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11471,7 +11474,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11479,6 +11481,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -11943,7 +11946,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -11951,6 +11953,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -13082,7 +13085,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -13090,6 +13092,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -16211,7 +16214,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -16219,6 +16221,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -17033,7 +17036,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -17041,6 +17043,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -17862,7 +17865,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -17870,6 +17872,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -20002,7 +20005,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -20010,6 +20012,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -22322,7 +22325,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -22330,6 +22332,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -24630,7 +24633,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -24638,6 +24640,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -26937,7 +26940,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -26945,6 +26947,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -39477,9 +39480,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -39517,9 +39520,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -39554,7 +39557,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -39589,7 +39592,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -40077,11 +40080,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5703125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="11.5703125" style="3"/>
+    <col min="1" max="16384" width="11.59765625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -40117,7 +40120,7 @@
       </c>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="12" t="s">
         <v>46</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -40155,7 +40158,7 @@
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="11">
+      <c r="A3" s="12">
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -40187,7 +40190,7 @@
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -40219,7 +40222,7 @@
       </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="11">
+      <c r="A5" s="12">
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -40251,7 +40254,7 @@
       </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="12" t="s">
         <v>44</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -40283,7 +40286,7 @@
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="11">
+      <c r="A7" s="12">
         <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -40315,7 +40318,7 @@
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="12" t="s">
         <v>43</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -40347,7 +40350,7 @@
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="11">
+      <c r="A9" s="12">
         <v>3</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -40379,7 +40382,7 @@
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -40411,7 +40414,7 @@
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="11">
+      <c r="A11" s="12">
         <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -40443,7 +40446,7 @@
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>41</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -40475,7 +40478,7 @@
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="11">
+      <c r="A13" s="12">
         <v>5</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -40507,7 +40510,7 @@
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -40527,7 +40530,7 @@
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="11">
+      <c r="A15" s="12">
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -40547,7 +40550,7 @@
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -40566,8 +40569,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="11">
+    <row r="17" spans="1:18">
+      <c r="A17" s="12">
         <v>7</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -40586,8 +40589,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:18">
+      <c r="A18" s="12" t="s">
         <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -40606,8 +40609,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="11">
+    <row r="19" spans="1:18">
+      <c r="A19" s="12">
         <v>8</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -40626,8 +40629,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:18">
+      <c r="A20" s="12" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -40646,8 +40649,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="11">
+    <row r="21" spans="1:18">
+      <c r="A21" s="12">
         <v>9</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -40666,8 +40669,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:18">
+      <c r="A22" s="12" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -40686,8 +40689,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="11">
+    <row r="23" spans="1:18">
+      <c r="A23" s="12">
         <v>10</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -40706,8 +40709,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="11" t="s">
+    <row r="24" spans="1:18">
+      <c r="A24" s="12" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -40726,8 +40729,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="11">
+    <row r="25" spans="1:18">
+      <c r="A25" s="12">
         <v>11</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -40746,37 +40749,38 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:18">
       <c r="A26" s="3" t="s">
         <v>46</v>
       </c>
+      <c r="R26" s="15"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:18">
       <c r="A27" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:18">
       <c r="A28" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:18">
       <c r="A29" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:18">
       <c r="A30" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:18">
       <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:18">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -40807,25 +40811,25 @@
       </c>
     </row>
     <row r="43" spans="1:17">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="12"/>
-      <c r="P43" s="12"/>
-      <c r="Q43" s="12"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="1" t="s">
@@ -41517,8 +41521,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F25"/>
+  <autoFilter ref="A1:F25" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="13">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
     <mergeCell ref="A43:Q43"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="A12:A13"/>
@@ -41527,11 +41536,6 @@
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -41544,9 +41548,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:S121"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
@@ -48569,66 +48573,66 @@
     </row>
   </sheetData>
   <mergeCells count="60">
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="A114:A115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="A118:A119"/>
+    <mergeCell ref="A120:A121"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A106:A107"/>
+    <mergeCell ref="A108:A109"/>
+    <mergeCell ref="A110:A111"/>
+    <mergeCell ref="A92:A93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:A99"/>
+    <mergeCell ref="A100:A101"/>
+    <mergeCell ref="A82:A83"/>
+    <mergeCell ref="A84:A85"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="A88:A89"/>
+    <mergeCell ref="A90:A91"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="A82:A83"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="A90:A91"/>
-    <mergeCell ref="A92:A93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:A99"/>
-    <mergeCell ref="A100:A101"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A106:A107"/>
-    <mergeCell ref="A108:A109"/>
-    <mergeCell ref="A110:A111"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="A114:A115"/>
-    <mergeCell ref="A116:A117"/>
-    <mergeCell ref="A118:A119"/>
-    <mergeCell ref="A120:A121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -48636,9 +48640,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S70"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:19">
       <c r="A1" s="13" t="s">
@@ -50039,11 +50043,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="A1:S1"/>
     <mergeCell ref="A50:A54"/>
     <mergeCell ref="A55:A59"/>
     <mergeCell ref="A60:A65"/>
@@ -50052,6 +50051,11 @@
     <mergeCell ref="A32:A36"/>
     <mergeCell ref="A37:A41"/>
     <mergeCell ref="A42:A46"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -50059,9 +50063,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -50296,9 +50300,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -51125,9 +51129,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="13" t="s">
@@ -51373,9 +51377,9 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:C63"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
@@ -51763,9 +51767,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E60"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="3"/>
   </cols>
@@ -52798,13 +52802,13 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.73046875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="7" width="11.42578125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" style="7" customWidth="1"/>
-    <col min="9" max="16384" width="10.7109375" style="7"/>
+    <col min="1" max="7" width="11.3984375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="10.73046875" style="7" customWidth="1"/>
+    <col min="9" max="16384" width="10.73046875" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -53106,9 +53110,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -53302,26 +53309,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671CA003-5E51-443F-BD9C-E3C60FBB189A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FD29CCB-4056-46E1-9298-4D3A656E9693}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="aee1ceab-3eaf-454d-9f8e-d2ca908d7479"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -53345,9 +53341,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5FD29CCB-4056-46E1-9298-4D3A656E9693}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{671CA003-5E51-443F-BD9C-E3C60FBB189A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="aee1ceab-3eaf-454d-9f8e-d2ca908d7479"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>